--- a/data/gravel/Planet X Tempest 2025.xlsx
+++ b/data/gravel/Planet X Tempest 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B7AFEA-99F7-1348-8095-D892CA4EE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A03897C-CE73-E644-A8AE-F682522B60C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2980" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28520" yWindow="-16980" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>external</t>
+  </si>
+  <si>
+    <t>https://img-va.myshopline.com/image/store/1704903372076/P1-Tempest-APEX-XPLR_1445x.jpeg?w=4424&amp;h=2460</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -438,10 +441,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,6 +787,11 @@
         <v>81</v>
       </c>
     </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>5</v>
@@ -797,7 +804,7 @@
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="10" t="s">

--- a/data/gravel/Planet X Tempest 2025.xlsx
+++ b/data/gravel/Planet X Tempest 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A03897C-CE73-E644-A8AE-F682522B60C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E29AC-7D27-2644-8BA8-6C3B7CABB7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28520" yWindow="-16980" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6580" yWindow="900" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -257,9 +257,6 @@
     <t>bb_height</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>gravel</t>
   </si>
   <si>
@@ -336,6 +333,15 @@
   </si>
   <si>
     <t>https://img-va.myshopline.com/image/store/1704903372076/P1-Tempest-APEX-XPLR_1445x.jpeg?w=4424&amp;h=2460</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Rotherham, South Yorkshire, United Kingdom</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -740,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -752,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -760,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -784,12 +790,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -797,7 +803,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20" customHeight="1">
@@ -805,22 +811,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="H8"/>
     </row>
@@ -829,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="12">
         <v>70.5</v>
@@ -853,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="12">
         <v>100</v>
@@ -876,7 +882,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="12">
         <v>520</v>
@@ -899,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="12">
         <v>74.5</v>
@@ -922,7 +928,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="12">
         <v>460</v>
@@ -945,7 +951,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="12">
         <v>440</v>
@@ -968,7 +974,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="12">
         <v>70</v>
@@ -991,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="12">
         <v>532</v>
@@ -1014,7 +1020,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="12">
         <v>373</v>
@@ -1037,7 +1043,7 @@
         <v>72</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="12">
         <v>588</v>
@@ -1060,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="12">
         <v>1018</v>
@@ -1328,7 +1334,7 @@
         <v>66</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1336,7 +1342,7 @@
         <v>67</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1362,7 +1368,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1488,7 +1494,7 @@
         <v>51</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1570,7 +1576,15 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>74</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Planet X Tempest 2025.xlsx
+++ b/data/gravel/Planet X Tempest 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E29AC-7D27-2644-8BA8-6C3B7CABB7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D66A453-556A-7C42-B845-7A21B293F7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="900" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -746,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1440,150 +1458,180 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="1">
-        <v>27.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1946</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>101</v>
       </c>
     </row>
